--- a/RAMON FRANCO/Mayo/PRORRATEO-RAMON-FRANCO-MAYO.xlsx
+++ b/RAMON FRANCO/Mayo/PRORRATEO-RAMON-FRANCO-MAYO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50841A7-70B3-48ED-BC56-4CB9F4BF896A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793C9318-C3ED-4162-8602-1DF72A11252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="84">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -277,10 +277,7 @@
     <t>GISELA</t>
   </si>
   <si>
-    <t>ESTE MES SE PRORRATEA DE FORMA ORDINARIA EL MISMO MONTO DEL MES ANTERIOR (A PESAR DE HABER GASTADO MAS DINERO) CON EL FIN DE SOSTENER LAS EXPENSAS EN UN NIVEL OPTIMO</t>
-  </si>
-  <si>
-    <t>EXPENSAS - VENCIMIENTO 14/05 LIQUIDACION : ABRIL</t>
+    <t>EXPENSAS - VENCIMIENTO 16/06 LIQUIDACION : MAYO</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1215,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -1358,9 +1355,7 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
-      <c r="C10" s="51">
-        <v>500000</v>
-      </c>
+      <c r="C10" s="51"/>
       <c r="D10" s="51"/>
       <c r="E10" s="38"/>
       <c r="F10" s="18"/>
@@ -1440,7 +1435,7 @@
         <v>7.99</v>
       </c>
       <c r="F12" s="58">
-        <v>73694.213342000003</v>
+        <v>183031.67816936001</v>
       </c>
       <c r="G12" s="44">
         <v>0</v>
@@ -1452,16 +1447,16 @@
       </c>
       <c r="J12" s="44">
         <f t="shared" ref="J12:J19" si="0">F12-G12-H12</f>
-        <v>73694.213342000003</v>
+        <v>183031.67816936001</v>
       </c>
       <c r="K12" s="44"/>
       <c r="L12" s="45">
         <f>(J12+K12)*8%</f>
-        <v>5895.53706736</v>
+        <v>14642.534253548802</v>
       </c>
       <c r="M12" s="45">
         <f>J12+L12+K12</f>
-        <v>79589.75040936</v>
+        <v>197674.21242290881</v>
       </c>
       <c r="N12" s="44">
         <f>C7*E12/100</f>
@@ -1469,11 +1464,11 @@
       </c>
       <c r="O12" s="44">
         <f t="shared" ref="O12:O29" si="1">C$10*E12/100</f>
-        <v>39950</v>
+        <v>0</v>
       </c>
       <c r="P12" s="45">
         <f>N12+M12+O12</f>
-        <v>183031.67816936001</v>
+        <v>261166.1401829088</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1493,28 +1488,30 @@
         <v>6.05</v>
       </c>
       <c r="F13" s="58">
-        <v>95601.160187200003</v>
+        <v>181575.118202176</v>
       </c>
       <c r="G13" s="44">
         <v>0</v>
       </c>
-      <c r="H13" s="69"/>
+      <c r="H13" s="69">
+        <v>30250</v>
+      </c>
       <c r="I13" s="44" t="e">
         <f>C9*E13/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J13" s="44">
         <f>F13-G13-H13</f>
-        <v>95601.160187200003</v>
+        <v>151325.118202176</v>
       </c>
       <c r="K13" s="44"/>
       <c r="L13" s="45">
         <f t="shared" ref="L13:L29" si="2">(J13+K13)*8%</f>
-        <v>7648.0928149760002</v>
+        <v>12106.009456174081</v>
       </c>
       <c r="M13" s="45">
         <f t="shared" ref="M13:M15" si="3">J13+L13+K13</f>
-        <v>103249.253002176</v>
+        <v>163431.12765835007</v>
       </c>
       <c r="N13" s="44">
         <f>C7*E13/100</f>
@@ -1522,11 +1519,11 @@
       </c>
       <c r="O13" s="44">
         <f t="shared" si="1"/>
-        <v>30250</v>
+        <v>0</v>
       </c>
       <c r="P13" s="45">
         <f t="shared" ref="P13:P29" si="4">N13+M13+O13</f>
-        <v>181575.118202176</v>
+        <v>211506.99285835007</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1546,14 +1543,14 @@
         <v>6.02</v>
       </c>
       <c r="F14" s="58">
-        <v>55524.300915999993</v>
+        <v>77937.472479999997</v>
       </c>
       <c r="G14" s="44">
         <v>0</v>
       </c>
       <c r="H14" s="69">
         <f t="shared" ref="H14:H29" si="5">F14</f>
-        <v>55524.300915999993</v>
+        <v>77937.472479999997</v>
       </c>
       <c r="I14" s="44" t="e">
         <f>C9*E14/100</f>
@@ -1578,11 +1575,11 @@
       </c>
       <c r="O14" s="44">
         <f t="shared" si="1"/>
-        <v>30100</v>
+        <v>0</v>
       </c>
       <c r="P14" s="45">
         <f t="shared" si="4"/>
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1600,12 +1597,12 @@
         <v>7.63</v>
       </c>
       <c r="F15" s="60">
-        <v>70373.823253999988</v>
+        <v>98781.215120000008</v>
       </c>
       <c r="G15" s="46"/>
       <c r="H15" s="69">
         <f>F15</f>
-        <v>70373.823253999988</v>
+        <v>98781.215120000008</v>
       </c>
       <c r="I15" s="44" t="e">
         <f>C9*E15/100</f>
@@ -1630,11 +1627,11 @@
       </c>
       <c r="O15" s="44">
         <f t="shared" si="1"/>
-        <v>38150</v>
+        <v>0</v>
       </c>
       <c r="P15" s="45">
         <f t="shared" si="4"/>
-        <v>98781.215120000008</v>
+        <v>60631.215120000001</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1654,14 +1651,13 @@
         <v>6.05</v>
       </c>
       <c r="F16" s="58">
-        <v>97378.840187199996</v>
+        <v>121718.10519999999</v>
       </c>
       <c r="G16" s="46">
         <v>0</v>
       </c>
       <c r="H16" s="69">
-        <f>F16-40178</f>
-        <v>57200.840187199996</v>
+        <v>30250</v>
       </c>
       <c r="I16" s="44" t="e">
         <f>C9*E16/100</f>
@@ -1669,16 +1665,16 @@
       </c>
       <c r="J16" s="44">
         <f t="shared" si="0"/>
-        <v>40178</v>
+        <v>91468.105199999991</v>
       </c>
       <c r="K16" s="44"/>
       <c r="L16" s="45">
         <f t="shared" si="2"/>
-        <v>3214.2400000000002</v>
+        <v>7317.4484159999993</v>
       </c>
       <c r="M16" s="45">
         <f>J16+L16+K16</f>
-        <v>43392.24</v>
+        <v>98785.55361599999</v>
       </c>
       <c r="N16" s="44">
         <f>C7*E16/100</f>
@@ -1686,11 +1682,11 @@
       </c>
       <c r="O16" s="44">
         <f t="shared" si="1"/>
-        <v>30250</v>
+        <v>0</v>
       </c>
       <c r="P16" s="45">
         <f t="shared" si="4"/>
-        <v>121718.10519999999</v>
+        <v>146861.41881599999</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1710,14 +1706,14 @@
         <v>6.02</v>
       </c>
       <c r="F17" s="58">
-        <v>96895.969905279999</v>
+        <v>77937.472479999997</v>
       </c>
       <c r="G17" s="44">
         <v>0</v>
       </c>
       <c r="H17" s="69">
         <f>F17</f>
-        <v>96895.969905279999</v>
+        <v>77937.472479999997</v>
       </c>
       <c r="I17" s="44" t="e">
         <f>C9*E17/100</f>
@@ -1742,11 +1738,11 @@
       </c>
       <c r="O17" s="44">
         <f t="shared" si="1"/>
-        <v>30100</v>
+        <v>0</v>
       </c>
       <c r="P17" s="45">
         <f t="shared" si="4"/>
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1764,14 +1760,14 @@
         <v>7.63</v>
       </c>
       <c r="F18" s="58">
-        <v>70373.823253999988</v>
+        <v>98781.215120000008</v>
       </c>
       <c r="G18" s="44">
         <v>0</v>
       </c>
       <c r="H18" s="69">
         <f t="shared" si="5"/>
-        <v>70373.823253999988</v>
+        <v>98781.215120000008</v>
       </c>
       <c r="I18" s="44" t="e">
         <f>C9*E18/100</f>
@@ -1796,11 +1792,11 @@
       </c>
       <c r="O18" s="44">
         <f t="shared" si="1"/>
-        <v>38150</v>
+        <v>0</v>
       </c>
       <c r="P18" s="45">
         <f t="shared" si="4"/>
-        <v>98781.215120000008</v>
+        <v>60631.215120000001</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1820,13 +1816,13 @@
         <v>6.05</v>
       </c>
       <c r="F19" s="58">
-        <v>130516.6575128487</v>
+        <v>177706.01531387659</v>
       </c>
       <c r="G19" s="44">
         <v>0</v>
       </c>
       <c r="H19" s="69">
-        <v>38498</v>
+        <v>48075.865199999993</v>
       </c>
       <c r="I19" s="44" t="e">
         <f>C9*E19/100</f>
@@ -1834,16 +1830,16 @@
       </c>
       <c r="J19" s="44">
         <f t="shared" si="0"/>
-        <v>92018.657512848702</v>
+        <v>129630.15011387659</v>
       </c>
       <c r="K19" s="44"/>
       <c r="L19" s="45">
         <f t="shared" si="2"/>
-        <v>7361.4926010278959</v>
+        <v>10370.412009110127</v>
       </c>
       <c r="M19" s="45">
         <f t="shared" si="6"/>
-        <v>99380.150113876603</v>
+        <v>140000.56212298671</v>
       </c>
       <c r="N19" s="44">
         <f>C7*E19/100</f>
@@ -1851,11 +1847,11 @@
       </c>
       <c r="O19" s="44">
         <f t="shared" si="1"/>
-        <v>30250</v>
+        <v>0</v>
       </c>
       <c r="P19" s="45">
         <f>N19+M19+O19</f>
-        <v>177706.01531387659</v>
+        <v>188076.42732298671</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1873,14 +1869,14 @@
         <v>6.02</v>
       </c>
       <c r="F20" s="58">
-        <v>55524.300915999993</v>
+        <v>77937.472479999997</v>
       </c>
       <c r="G20" s="44">
         <v>0</v>
       </c>
       <c r="H20" s="69">
         <f t="shared" si="5"/>
-        <v>55524.300915999993</v>
+        <v>77937.472479999997</v>
       </c>
       <c r="I20" s="44" t="e">
         <f>C9*E20/100</f>
@@ -1905,11 +1901,11 @@
       </c>
       <c r="O20" s="44">
         <f t="shared" si="1"/>
-        <v>30100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="45">
         <f t="shared" si="4"/>
-        <v>77937.472479999997</v>
+        <v>47837.472479999997</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1927,14 +1923,14 @@
         <v>21.2</v>
       </c>
       <c r="F21" s="58">
-        <v>195534.08295999997</v>
+        <v>274464.1888</v>
       </c>
       <c r="G21" s="44">
         <v>0</v>
       </c>
       <c r="H21" s="69">
         <f>F21</f>
-        <v>195534.08295999997</v>
+        <v>274464.1888</v>
       </c>
       <c r="I21" s="44" t="e">
         <f>C9*E21/100</f>
@@ -1959,11 +1955,11 @@
       </c>
       <c r="O21" s="44">
         <f t="shared" si="1"/>
-        <v>106000</v>
+        <v>0</v>
       </c>
       <c r="P21" s="45">
         <f t="shared" si="4"/>
-        <v>274464.1888</v>
+        <v>168464.1888</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1983,14 +1979,14 @@
         <v>6.81</v>
       </c>
       <c r="F22" s="58">
-        <v>62810.712497999994</v>
+        <v>88165.147440000001</v>
       </c>
       <c r="G22" s="44">
         <v>0</v>
       </c>
       <c r="H22" s="69">
         <f>F22</f>
-        <v>62810.712497999994</v>
+        <v>88165.147440000001</v>
       </c>
       <c r="I22" s="44" t="e">
         <f>C9*E22/100</f>
@@ -2015,11 +2011,11 @@
       </c>
       <c r="O22" s="44">
         <f t="shared" si="1"/>
-        <v>34050</v>
+        <v>0</v>
       </c>
       <c r="P22" s="45">
         <f t="shared" si="4"/>
-        <v>88165.147440000001</v>
+        <v>54115.147440000001</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2039,30 +2035,29 @@
         <v>6.52</v>
       </c>
       <c r="F23" s="69">
-        <v>216586.7430887738</v>
+        <v>158652.84701587568</v>
       </c>
       <c r="G23" s="44">
         <v>0</v>
       </c>
       <c r="H23" s="69">
-        <f>356213-67851-65650-74868</f>
-        <v>147844</v>
+        <v>51811</v>
       </c>
       <c r="I23" s="44">
         <v>0</v>
       </c>
       <c r="J23" s="44">
         <f t="shared" si="7"/>
-        <v>68742.743088773801</v>
+        <v>106841.84701587568</v>
       </c>
       <c r="K23" s="44"/>
       <c r="L23" s="67">
         <f t="shared" si="2"/>
-        <v>5499.4194471019046</v>
+        <v>8547.3477612700553</v>
       </c>
       <c r="M23" s="67">
         <f>J23+L23+K23</f>
-        <v>74242.162535875701</v>
+        <v>115389.19477714573</v>
       </c>
       <c r="N23" s="44">
         <f>C7*E23/100</f>
@@ -2070,11 +2065,11 @@
       </c>
       <c r="O23" s="44">
         <f t="shared" si="1"/>
-        <v>32600</v>
+        <v>0</v>
       </c>
       <c r="P23" s="45">
         <f t="shared" si="4"/>
-        <v>158652.84701587568</v>
+        <v>167199.87925714575</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2092,30 +2087,28 @@
         <v>1.18</v>
       </c>
       <c r="F24" s="58">
-        <v>343648.24836767331</v>
+        <v>386416.88855708716</v>
       </c>
       <c r="G24" s="44">
         <v>0</v>
       </c>
-      <c r="H24" s="69">
-        <v>0</v>
-      </c>
+      <c r="H24" s="69"/>
       <c r="I24" s="44" t="e">
         <f>C9*E24/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J24" s="44">
         <f t="shared" si="7"/>
-        <v>343648.24836767331</v>
+        <v>386416.88855708716</v>
       </c>
       <c r="K24" s="44"/>
       <c r="L24" s="45">
         <f t="shared" si="2"/>
-        <v>27491.859869413864</v>
+        <v>30913.351084566973</v>
       </c>
       <c r="M24" s="45">
         <f t="shared" si="6"/>
-        <v>371140.10823708714</v>
+        <v>417330.23964165413</v>
       </c>
       <c r="N24" s="44">
         <f>C7*E24/100</f>
@@ -2123,11 +2116,11 @@
       </c>
       <c r="O24" s="44">
         <f t="shared" si="1"/>
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="P24" s="45">
         <f t="shared" si="4"/>
-        <v>386416.88855708716</v>
+        <v>426707.01996165415</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2145,7 +2138,7 @@
         <v>1.17</v>
       </c>
       <c r="F25" s="58">
-        <v>339023.80314834946</v>
+        <v>381293.02348021744</v>
       </c>
       <c r="G25" s="44">
         <v>0</v>
@@ -2159,16 +2152,16 @@
       </c>
       <c r="J25" s="44">
         <f t="shared" si="7"/>
-        <v>339023.80314834946</v>
+        <v>381293.02348021744</v>
       </c>
       <c r="K25" s="44"/>
       <c r="L25" s="45">
         <f t="shared" si="2"/>
-        <v>27121.904251867956</v>
+        <v>30503.441878417394</v>
       </c>
       <c r="M25" s="45">
         <f t="shared" si="6"/>
-        <v>366145.70740021742</v>
+        <v>411796.46535863483</v>
       </c>
       <c r="N25" s="44">
         <f>C7*E25/100</f>
@@ -2176,11 +2169,11 @@
       </c>
       <c r="O25" s="44">
         <f t="shared" si="1"/>
-        <v>5850</v>
+        <v>0</v>
       </c>
       <c r="P25" s="45">
         <f t="shared" si="4"/>
-        <v>381293.02348021744</v>
+        <v>421093.78143863485</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2198,14 +2191,14 @@
         <v>1.06</v>
       </c>
       <c r="F26" s="58">
-        <v>9776.7041480000007</v>
+        <v>13723.209440000001</v>
       </c>
       <c r="G26" s="44">
         <v>0</v>
       </c>
       <c r="H26" s="69">
         <f>F26</f>
-        <v>9776.7041480000007</v>
+        <v>13723.209440000001</v>
       </c>
       <c r="I26" s="44" t="e">
         <f>C9*E26/100</f>
@@ -2230,11 +2223,11 @@
       </c>
       <c r="O26" s="44">
         <f t="shared" si="1"/>
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="P26" s="45">
         <f t="shared" si="4"/>
-        <v>13723.209440000001</v>
+        <v>8423.2094400000005</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2252,7 +2245,7 @@
         <v>0.51</v>
       </c>
       <c r="F27" s="58">
-        <v>11994.096334051203</v>
+        <v>19556.3002807753</v>
       </c>
       <c r="G27" s="44">
         <v>0</v>
@@ -2264,16 +2257,16 @@
       </c>
       <c r="J27" s="44">
         <f t="shared" si="7"/>
-        <v>11994.096334051203</v>
+        <v>19556.3002807753</v>
       </c>
       <c r="K27" s="44"/>
       <c r="L27" s="45">
         <f t="shared" si="2"/>
-        <v>959.52770672409622</v>
+        <v>1564.5040224620241</v>
       </c>
       <c r="M27" s="45">
         <f t="shared" si="6"/>
-        <v>12953.624040775299</v>
+        <v>21120.804303237324</v>
       </c>
       <c r="N27" s="44">
         <f>C7*E27/100</f>
@@ -2281,11 +2274,11 @@
       </c>
       <c r="O27" s="44">
         <f t="shared" si="1"/>
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="P27" s="45">
         <f t="shared" si="4"/>
-        <v>19556.3002807753</v>
+        <v>25173.480543237325</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2303,14 +2296,14 @@
         <v>0.27</v>
       </c>
       <c r="F28" s="58">
-        <v>2490.2925660000001</v>
+        <v>3495.5344800000003</v>
       </c>
       <c r="G28" s="44">
         <v>0</v>
       </c>
       <c r="H28" s="69">
         <f t="shared" si="5"/>
-        <v>2490.2925660000001</v>
+        <v>3495.5344800000003</v>
       </c>
       <c r="I28" s="44" t="e">
         <f>C9*E28/100</f>
@@ -2335,11 +2328,11 @@
       </c>
       <c r="O28" s="44">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="P28" s="45">
         <f t="shared" si="4"/>
-        <v>3495.5344800000003</v>
+        <v>2145.5344800000003</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2355,14 +2348,14 @@
         <v>1.82</v>
       </c>
       <c r="F29" s="59">
-        <v>16786.416556</v>
+        <v>23562.491679999999</v>
       </c>
       <c r="G29" s="44">
         <v>0</v>
       </c>
       <c r="H29" s="69">
         <f t="shared" si="5"/>
-        <v>16786.416556</v>
+        <v>23562.491679999999</v>
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="44">
@@ -2384,11 +2377,11 @@
       </c>
       <c r="O29" s="44">
         <f t="shared" si="1"/>
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="P29" s="45">
         <f t="shared" si="4"/>
-        <v>23562.491679999999</v>
+        <v>14462.491680000001</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -2401,7 +2394,7 @@
       <c r="E30" s="42"/>
       <c r="F30" s="54">
         <f>SUM(F12:F29)</f>
-        <v>1944534.1891413766</v>
+        <v>2444735.3957393682</v>
       </c>
       <c r="G30" s="54">
         <f>SUM(G12:G29)</f>
@@ -2409,17 +2402,17 @@
       </c>
       <c r="H30" s="62">
         <f>SUM(H12:H29)</f>
-        <v>879633.26716047991</v>
+        <v>995172.28472</v>
       </c>
       <c r="I30" s="54"/>
       <c r="J30" s="62">
         <f>SUM(J12:J29)</f>
-        <v>1064900.9219808965</v>
+        <v>1449563.1110193683</v>
       </c>
       <c r="K30" s="54"/>
       <c r="L30" s="68">
         <f>L12+L13+L14+L15+L16+L17+L18+L19+L20+L21+L22+L23+L24+L25+L26+L27+L28+L29</f>
-        <v>85192.073758471728</v>
+        <v>115965.04888154946</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="70">
@@ -2428,11 +2421,11 @@
       </c>
       <c r="O30" s="56">
         <f>SUM(O12:O29)</f>
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="P30" s="57">
         <f>SUM(P16:P29) +P15+P14+P13+P12</f>
-        <v>2444735.3957393682</v>
+        <v>2360170.5599009176</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2466,9 +2459,7 @@
       <c r="K32" s="4"/>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="71" t="s">
-        <v>83</v>
-      </c>
+      <c r="B33" s="71"/>
       <c r="C33" s="71"/>
       <c r="D33" s="71"/>
       <c r="E33" s="71"/>

--- a/RAMON FRANCO/Mayo/PRORRATEO-RAMON-FRANCO-MAYO.xlsx
+++ b/RAMON FRANCO/Mayo/PRORRATEO-RAMON-FRANCO-MAYO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793C9318-C3ED-4162-8602-1DF72A11252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7928BEAE-2951-4420-8813-D08081EAA116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
